--- a/cloud-for-sovereignty/NIS2 (Preview)/NIS2_Mapping.xlsx
+++ b/cloud-for-sovereignty/NIS2 (Preview)/NIS2_Mapping.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28025"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://microsoft-my.sharepoint.com/personal/kanchauhan_microsoft_com/Documents/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="8_{03135850-6309-4832-9A89-9F1A59B4F8FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{196FEB65-0187-4405-B85F-B1E3EF158507}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DE3E4E3D-33E8-4CA3-91A3-F6297F7E0CEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="37320" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E68A5A7F-55A1-4D24-949C-D3EE6C027DDA}"/>
+    <workbookView xWindow="2280" yWindow="2280" windowWidth="18720" windowHeight="11650" xr2:uid="{5AB5E1DB-186B-4FB5-93F0-A5A9AF0585E2}"/>
   </bookViews>
   <sheets>
     <sheet name="PolicySetDefinitionMappings" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1779" uniqueCount="600">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1793" uniqueCount="604">
   <si>
     <t>Control ID</t>
   </si>
@@ -52,7 +52,7 @@
     <t>Risk analysis &amp; information system security policies</t>
   </si>
   <si>
-    <t>Responsibility for ensuring the security of network and information system lies, to a great extent, with essential and important entities. A culture of risk management, involving risk assessments and the implementation of cybersecurity risk-management measures appropriate to the risks faced, should be promoted and developed.
+    <t>Responsibility for ensuring the security of network and information system lies, to a great extent, with essential and important entities. A culture of risk management, involving risk assessments and the implementation of cybersecurity risk-management measures appropriate to the risks faced, should be promoted and developed._x000D_
 In order to avoid imposing a disproportionate financial and administrative burden on essential and important entities, the cybersecurity risk-management measures should be proportionate to the risks posed to the network and information system concerned, taking into account the state-of-the-art of such measures, and, where applicable, relevant European and international standards, as well as the cost for their implementation.</t>
   </si>
   <si>
@@ -914,12 +914,6 @@
     <t>/providers/Microsoft.Authorization/policyDefinitions/bb91dfba-c30d-4263-9add-9c2384e659a6</t>
   </si>
   <si>
-    <t>Adaptive network hardening recommendations should be applied on internet facing virtual machines</t>
-  </si>
-  <si>
-    <t>/providers/Microsoft.Authorization/policyDefinitions/08e6af2d-db70-460a-bfe9-d5bd474ba9d6</t>
-  </si>
-  <si>
     <t>Storage accounts should restrict network access using virtual network rules</t>
   </si>
   <si>
@@ -1028,12 +1022,6 @@
     <t>/providers/Microsoft.Authorization/policyDefinitions/6ba6d016-e7c3-4842-b8f2-4992ebc0d72d</t>
   </si>
   <si>
-    <t>System updates on virtual machine scale sets should be installed</t>
-  </si>
-  <si>
-    <t>/providers/Microsoft.Authorization/policyDefinitions/c3f317a7-a95c-4547-b7e7-11017ebdf2fe</t>
-  </si>
-  <si>
     <t>SQL databases should have vulnerability findings resolved</t>
   </si>
   <si>
@@ -1166,7 +1154,7 @@
     <t>Basic cybersecurity hygiene and training</t>
   </si>
   <si>
-    <t>Essential and important entities should adopt a wide range of basic cyber hygiene practices, such as zero-trust principles, software updates, device configuration, network segmentation, identity and access management or user awareness, organise training for their staff and raise awareness concerning cyber threats, phishing or social engineering techniques. 
+    <t>Essential and important entities should adopt a wide range of basic cyber hygiene practices, such as zero-trust principles, software updates, device configuration, network segmentation, identity and access management or user awareness, organise training for their staff and raise awareness concerning cyber threats, phishing or social engineering techniques. _x000D_
 Cyber hygiene policies provide the foundations for protecting network and information system infrastructures, hardware, software and online application security, and business or end-user data upon which entities rely. Cyber hygiene policies comprising a common baseline set of practices, including software and hardware updates, password changes, the management of new installs, the limitation of administrator-level access accounts, and the backing-up of data, enable a proactive framework of preparedness and overall safety and security in the event of incidents or cyber threats. ENISA should monitor and analyse Member Statesâ€™ cyber hygiene policies.</t>
   </si>
   <si>
@@ -1572,16 +1560,40 @@
     <t>/providers/Microsoft.Authorization/policyDefinitions/3aa03346-d8c5-4994-a5bc-7652c2a2aef1</t>
   </si>
   <si>
-    <t>Allowlist rules in your adaptive application control policy should be updated</t>
-  </si>
-  <si>
-    <t>/providers/Microsoft.Authorization/policyDefinitions/123a3936-f020-408a-ba0c-47873faf1534</t>
-  </si>
-  <si>
-    <t>Adaptive application controls for defining safe applications should be enabled on your machines</t>
-  </si>
-  <si>
-    <t>/providers/Microsoft.Authorization/policyDefinitions/47a6b606-51aa-4496-8bb7-64b11cf66adc</t>
+    <t>[Preview]: ChangeTracking extension should be installed on your Linux Arc machine</t>
+  </si>
+  <si>
+    <t>/providers/Microsoft.Authorization/policyDefinitions/fc47609f-4d9b-4aed-806b-446816cc63a3</t>
+  </si>
+  <si>
+    <t>[Preview]: ChangeTracking extension should be installed on your Linux virtual machine</t>
+  </si>
+  <si>
+    <t>/providers/Microsoft.Authorization/policyDefinitions/8893442c-e7cb-4637-bab8-299a5d4ed96a</t>
+  </si>
+  <si>
+    <t>[Preview]: ChangeTracking extension should be installed on your Linux virtual machine scale sets</t>
+  </si>
+  <si>
+    <t>/providers/Microsoft.Authorization/policyDefinitions/e71c1e29-9c76-4532-8c4b-cb0573b0014c</t>
+  </si>
+  <si>
+    <t>[Preview]: ChangeTracking extension should be installed on your Windows Arc machine</t>
+  </si>
+  <si>
+    <t>/providers/Microsoft.Authorization/policyDefinitions/a7f5e735-d212-4c32-9229-d12bffbc7e00</t>
+  </si>
+  <si>
+    <t>[Preview]: ChangeTracking extension should be installed on your Windows virtual machine</t>
+  </si>
+  <si>
+    <t>/providers/Microsoft.Authorization/policyDefinitions/221aac80-54d8-484b-83d7-24f4feac2ce0</t>
+  </si>
+  <si>
+    <t>[Preview]: ChangeTracking extension should be installed on your Windows virtual machine scale sets</t>
+  </si>
+  <si>
+    <t>/providers/Microsoft.Authorization/policyDefinitions/4bb303db-d051-4099-95d2-e3e1428a4d00</t>
   </si>
   <si>
     <t>IM. Identity Management</t>
@@ -2369,17 +2381,17 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00C65412-BE59-414E-92D7-7EF682868E5D}" name="Table1" displayName="Table1" ref="A1:H254" totalsRowShown="0">
-  <autoFilter ref="A1:H254" xr:uid="{00C65412-BE59-414E-92D7-7EF682868E5D}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{74129540-B4FD-48C0-8300-DEBC7D8F084B}" name="Table1" displayName="Table1" ref="A1:H256" totalsRowShown="0">
+  <autoFilter ref="A1:H256" xr:uid="{74129540-B4FD-48C0-8300-DEBC7D8F084B}"/>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{2F8160D6-E654-491B-AB76-A815139AB26C}" name="Control ID"/>
-    <tableColumn id="2" xr3:uid="{D6252F71-2A7D-4936-893C-7834F6014298}" name="Control Domain"/>
-    <tableColumn id="3" xr3:uid="{C4C37545-366F-4E4B-8EA8-707C27BCEB0B}" name="Control Title"/>
-    <tableColumn id="4" xr3:uid="{6A2BE561-3E6D-4D4A-AFE7-FBDA2E8C997B}" name="Control Description"/>
-    <tableColumn id="5" xr3:uid="{FC3DE25A-E7C9-4D27-81E1-92DFC00A1FB8}" name="Azure Policy Display Name"/>
-    <tableColumn id="6" xr3:uid="{68A54D50-48B7-4857-B0C8-85A4E052EA46}" name="Policiy Definition Reference ID"/>
-    <tableColumn id="7" xr3:uid="{F5025EE3-0F32-4EC2-90DC-C0B42B8DCA89}" name="Policy Definition ID"/>
-    <tableColumn id="8" xr3:uid="{C81C2ACC-3141-4C15-A25D-E6B83728F818}" name="Owner"/>
+    <tableColumn id="1" xr3:uid="{992702D3-D055-4302-A04C-7542C5F8C629}" name="Control ID"/>
+    <tableColumn id="2" xr3:uid="{CA3A4AF7-D4BA-4029-9930-59F192FE2A05}" name="Control Domain"/>
+    <tableColumn id="3" xr3:uid="{BEE1AEFF-597F-4708-86D2-2934ADA06A69}" name="Control Title"/>
+    <tableColumn id="4" xr3:uid="{70FA08D4-1B74-43A6-8EDE-CEC53F09B01A}" name="Control Description"/>
+    <tableColumn id="5" xr3:uid="{43DB9960-AEA2-4092-B62A-74C6DFCFCC7C}" name="Azure Policy Display Name"/>
+    <tableColumn id="6" xr3:uid="{A51B36EF-1FDE-4CE9-9E55-831A42D6EF73}" name="Policiy Definition Reference ID"/>
+    <tableColumn id="7" xr3:uid="{A7D0890D-A27B-4B36-BA73-37809AD651BE}" name="Policy Definition ID"/>
+    <tableColumn id="8" xr3:uid="{E11C9360-DFCF-4053-8887-4B00D3026E29}" name="Owner"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2701,17 +2713,18 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{07F55939-596C-416A-88DB-7DD651BDF227}">
-  <dimension ref="A1:H254"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A50AAF6F-FFCB-4EC9-8854-C3D74C2F543E}">
+  <dimension ref="A1:H256"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="11.7265625" customWidth="1"/>
-    <col min="2" max="2" width="16.54296875" customWidth="1"/>
-    <col min="3" max="3" width="13.6328125" customWidth="1"/>
-    <col min="4" max="4" width="19.90625" customWidth="1"/>
-    <col min="5" max="5" width="25.54296875" customWidth="1"/>
-    <col min="6" max="6" width="29.453125" customWidth="1"/>
-    <col min="7" max="7" width="19.54296875" customWidth="1"/>
+    <col min="1" max="1" width="11.1796875" customWidth="1"/>
+    <col min="2" max="2" width="29.81640625" customWidth="1"/>
+    <col min="3" max="3" width="46.36328125" customWidth="1"/>
+    <col min="4" max="4" width="29.36328125" customWidth="1"/>
+    <col min="5" max="5" width="24.81640625" customWidth="1"/>
+    <col min="6" max="6" width="28.26953125" customWidth="1"/>
+    <col min="7" max="7" width="32.81640625" customWidth="1"/>
+    <col min="8" max="8" width="22.90625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.35">
@@ -6108,13 +6121,13 @@
         <v>59</v>
       </c>
       <c r="E131" t="s">
-        <v>315</v>
+        <v>222</v>
       </c>
       <c r="F131" t="s">
         <v>315</v>
       </c>
       <c r="G131" t="s">
-        <v>316</v>
+        <v>223</v>
       </c>
       <c r="H131" t="s">
         <v>59</v>
@@ -6134,13 +6147,13 @@
         <v>59</v>
       </c>
       <c r="E132" t="s">
-        <v>222</v>
+        <v>316</v>
       </c>
       <c r="F132" t="s">
+        <v>316</v>
+      </c>
+      <c r="G132" t="s">
         <v>317</v>
-      </c>
-      <c r="G132" t="s">
-        <v>223</v>
       </c>
       <c r="H132" t="s">
         <v>59</v>
@@ -6293,10 +6306,10 @@
         <v>328</v>
       </c>
       <c r="F138" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="G138" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H138" t="s">
         <v>59</v>
@@ -6316,7 +6329,7 @@
         <v>59</v>
       </c>
       <c r="E139" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="F139" t="s">
         <v>331</v>
@@ -6408,54 +6421,54 @@
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A143">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B143" t="s">
-        <v>234</v>
+        <v>339</v>
       </c>
       <c r="C143" t="s">
-        <v>235</v>
+        <v>340</v>
       </c>
       <c r="D143" t="s">
-        <v>59</v>
+        <v>341</v>
       </c>
       <c r="E143" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="F143" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="G143" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="H143" t="s">
-        <v>59</v>
+        <v>13</v>
       </c>
     </row>
     <row r="144" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A144">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B144" t="s">
-        <v>234</v>
+        <v>339</v>
       </c>
       <c r="C144" t="s">
-        <v>235</v>
+        <v>340</v>
       </c>
       <c r="D144" t="s">
-        <v>59</v>
+        <v>341</v>
       </c>
       <c r="E144" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="F144" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="G144" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="H144" t="s">
-        <v>59</v>
+        <v>178</v>
       </c>
     </row>
     <row r="145" spans="1:8" x14ac:dyDescent="0.35">
@@ -6463,16 +6476,16 @@
         <v>6</v>
       </c>
       <c r="B145" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="C145" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="D145" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="E145" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="F145" t="s">
         <v>347</v>
@@ -6489,25 +6502,25 @@
         <v>6</v>
       </c>
       <c r="B146" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="C146" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="D146" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="E146" t="s">
-        <v>349</v>
+        <v>14</v>
       </c>
       <c r="F146" t="s">
         <v>349</v>
       </c>
       <c r="G146" t="s">
-        <v>350</v>
+        <v>15</v>
       </c>
       <c r="H146" t="s">
-        <v>178</v>
+        <v>13</v>
       </c>
     </row>
     <row r="147" spans="1:8" x14ac:dyDescent="0.35">
@@ -6515,22 +6528,22 @@
         <v>6</v>
       </c>
       <c r="B147" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="C147" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="D147" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="E147" t="s">
-        <v>351</v>
+        <v>26</v>
       </c>
       <c r="F147" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="G147" t="s">
-        <v>352</v>
+        <v>27</v>
       </c>
       <c r="H147" t="s">
         <v>13</v>
@@ -6541,22 +6554,22 @@
         <v>6</v>
       </c>
       <c r="B148" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="C148" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="D148" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="E148" t="s">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="F148" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="G148" t="s">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="H148" t="s">
         <v>13</v>
@@ -6567,22 +6580,22 @@
         <v>6</v>
       </c>
       <c r="B149" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="C149" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="D149" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="E149" t="s">
-        <v>26</v>
+        <v>352</v>
       </c>
       <c r="F149" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="G149" t="s">
-        <v>27</v>
+        <v>353</v>
       </c>
       <c r="H149" t="s">
         <v>13</v>
@@ -6593,22 +6606,22 @@
         <v>6</v>
       </c>
       <c r="B150" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="C150" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="D150" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="E150" t="s">
-        <v>30</v>
+        <v>354</v>
       </c>
       <c r="F150" t="s">
+        <v>354</v>
+      </c>
+      <c r="G150" t="s">
         <v>355</v>
-      </c>
-      <c r="G150" t="s">
-        <v>31</v>
       </c>
       <c r="H150" t="s">
         <v>13</v>
@@ -6619,13 +6632,13 @@
         <v>6</v>
       </c>
       <c r="B151" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="C151" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="D151" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="E151" t="s">
         <v>356</v>
@@ -6645,13 +6658,13 @@
         <v>6</v>
       </c>
       <c r="B152" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="C152" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="D152" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="E152" t="s">
         <v>358</v>
@@ -6671,22 +6684,22 @@
         <v>6</v>
       </c>
       <c r="B153" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="C153" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="D153" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="E153" t="s">
         <v>360</v>
       </c>
       <c r="F153" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="G153" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="H153" t="s">
         <v>13</v>
@@ -6697,25 +6710,25 @@
         <v>6</v>
       </c>
       <c r="B154" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="C154" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="D154" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="E154" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="F154" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="G154" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H154" t="s">
-        <v>13</v>
+        <v>187</v>
       </c>
     </row>
     <row r="155" spans="1:8" x14ac:dyDescent="0.35">
@@ -6723,16 +6736,16 @@
         <v>6</v>
       </c>
       <c r="B155" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="C155" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="D155" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="E155" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F155" t="s">
         <v>365</v>
@@ -6741,7 +6754,7 @@
         <v>366</v>
       </c>
       <c r="H155" t="s">
-        <v>13</v>
+        <v>187</v>
       </c>
     </row>
     <row r="156" spans="1:8" x14ac:dyDescent="0.35">
@@ -6749,13 +6762,13 @@
         <v>6</v>
       </c>
       <c r="B156" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="C156" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="D156" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="E156" t="s">
         <v>367</v>
@@ -6775,13 +6788,13 @@
         <v>6</v>
       </c>
       <c r="B157" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="C157" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="D157" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="E157" t="s">
         <v>369</v>
@@ -6801,13 +6814,13 @@
         <v>6</v>
       </c>
       <c r="B158" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="C158" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="D158" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="E158" t="s">
         <v>371</v>
@@ -6827,13 +6840,13 @@
         <v>6</v>
       </c>
       <c r="B159" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="C159" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="D159" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="E159" t="s">
         <v>373</v>
@@ -6850,54 +6863,54 @@
     </row>
     <row r="160" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A160">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B160" t="s">
-        <v>343</v>
+        <v>375</v>
       </c>
       <c r="C160" t="s">
-        <v>344</v>
-      </c>
-      <c r="D160" t="s">
-        <v>345</v>
+        <v>376</v>
+      </c>
+      <c r="D160" s="1" t="s">
+        <v>377</v>
       </c>
       <c r="E160" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="F160" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="G160" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="H160" t="s">
-        <v>187</v>
+        <v>13</v>
       </c>
     </row>
     <row r="161" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A161">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B161" t="s">
-        <v>343</v>
+        <v>375</v>
       </c>
       <c r="C161" t="s">
-        <v>344</v>
-      </c>
-      <c r="D161" t="s">
-        <v>345</v>
+        <v>376</v>
+      </c>
+      <c r="D161" s="1" t="s">
+        <v>377</v>
       </c>
       <c r="E161" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="F161" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="G161" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="H161" t="s">
-        <v>187</v>
+        <v>13</v>
       </c>
     </row>
     <row r="162" spans="1:8" x14ac:dyDescent="0.35">
@@ -6905,13 +6918,13 @@
         <v>7</v>
       </c>
       <c r="B162" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="C162" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="E162" t="s">
         <v>382</v>
@@ -6931,22 +6944,22 @@
         <v>7</v>
       </c>
       <c r="B163" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="C163" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="E163" t="s">
         <v>384</v>
       </c>
       <c r="F163" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="G163" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H163" t="s">
         <v>13</v>
@@ -6957,22 +6970,22 @@
         <v>7</v>
       </c>
       <c r="B164" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="C164" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="E164" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="F164" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="G164" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H164" t="s">
         <v>13</v>
@@ -6983,22 +6996,22 @@
         <v>7</v>
       </c>
       <c r="B165" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="C165" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="E165" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="F165" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="G165" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H165" t="s">
         <v>13</v>
@@ -7009,22 +7022,22 @@
         <v>7</v>
       </c>
       <c r="B166" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="C166" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="E166" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="F166" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="G166" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="H166" t="s">
         <v>13</v>
@@ -7035,22 +7048,22 @@
         <v>7</v>
       </c>
       <c r="B167" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="C167" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="E167" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="F167" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="G167" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H167" t="s">
         <v>13</v>
@@ -7058,25 +7071,25 @@
     </row>
     <row r="168" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A168">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B168" t="s">
-        <v>379</v>
+        <v>397</v>
       </c>
       <c r="C168" t="s">
-        <v>380</v>
-      </c>
-      <c r="D168" s="1" t="s">
-        <v>381</v>
+        <v>398</v>
+      </c>
+      <c r="D168" t="s">
+        <v>399</v>
       </c>
       <c r="E168" t="s">
-        <v>396</v>
+        <v>150</v>
       </c>
       <c r="F168" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="G168" t="s">
-        <v>398</v>
+        <v>151</v>
       </c>
       <c r="H168" t="s">
         <v>13</v>
@@ -7084,25 +7097,25 @@
     </row>
     <row r="169" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A169">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B169" t="s">
-        <v>379</v>
+        <v>397</v>
       </c>
       <c r="C169" t="s">
-        <v>380</v>
-      </c>
-      <c r="D169" s="1" t="s">
-        <v>381</v>
+        <v>398</v>
+      </c>
+      <c r="D169" t="s">
+        <v>399</v>
       </c>
       <c r="E169" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="F169" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="G169" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="H169" t="s">
         <v>13</v>
@@ -7113,22 +7126,22 @@
         <v>8</v>
       </c>
       <c r="B170" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="C170" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="D170" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="E170" t="s">
-        <v>150</v>
+        <v>404</v>
       </c>
       <c r="F170" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="G170" t="s">
-        <v>151</v>
+        <v>406</v>
       </c>
       <c r="H170" t="s">
         <v>13</v>
@@ -7139,22 +7152,22 @@
         <v>8</v>
       </c>
       <c r="B171" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="C171" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="D171" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="E171" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="F171" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="G171" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="H171" t="s">
         <v>13</v>
@@ -7165,25 +7178,25 @@
         <v>8</v>
       </c>
       <c r="B172" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="C172" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="D172" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="E172" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="F172" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="G172" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="H172" t="s">
-        <v>13</v>
+        <v>178</v>
       </c>
     </row>
     <row r="173" spans="1:8" x14ac:dyDescent="0.35">
@@ -7191,22 +7204,22 @@
         <v>8</v>
       </c>
       <c r="B173" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="C173" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="D173" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="E173" t="s">
-        <v>411</v>
+        <v>352</v>
       </c>
       <c r="F173" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="G173" t="s">
-        <v>413</v>
+        <v>353</v>
       </c>
       <c r="H173" t="s">
         <v>13</v>
@@ -7217,25 +7230,25 @@
         <v>8</v>
       </c>
       <c r="B174" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="C174" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="D174" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="E174" t="s">
         <v>414</v>
       </c>
       <c r="F174" t="s">
+        <v>414</v>
+      </c>
+      <c r="G174" t="s">
         <v>415</v>
       </c>
-      <c r="G174" t="s">
-        <v>416</v>
-      </c>
       <c r="H174" t="s">
-        <v>178</v>
+        <v>13</v>
       </c>
     </row>
     <row r="175" spans="1:8" x14ac:dyDescent="0.35">
@@ -7243,25 +7256,25 @@
         <v>8</v>
       </c>
       <c r="B175" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="C175" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="D175" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="E175" t="s">
-        <v>356</v>
+        <v>416</v>
       </c>
       <c r="F175" t="s">
+        <v>416</v>
+      </c>
+      <c r="G175" t="s">
         <v>417</v>
       </c>
-      <c r="G175" t="s">
-        <v>357</v>
-      </c>
       <c r="H175" t="s">
-        <v>13</v>
+        <v>187</v>
       </c>
     </row>
     <row r="176" spans="1:8" x14ac:dyDescent="0.35">
@@ -7269,22 +7282,22 @@
         <v>8</v>
       </c>
       <c r="B176" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="C176" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="D176" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="E176" t="s">
         <v>418</v>
       </c>
       <c r="F176" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="G176" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="H176" t="s">
         <v>13</v>
@@ -7295,25 +7308,25 @@
         <v>8</v>
       </c>
       <c r="B177" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="C177" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="D177" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="E177" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="F177" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="G177" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="H177" t="s">
-        <v>187</v>
+        <v>13</v>
       </c>
     </row>
     <row r="178" spans="1:8" x14ac:dyDescent="0.35">
@@ -7321,22 +7334,22 @@
         <v>8</v>
       </c>
       <c r="B178" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="C178" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="D178" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="E178" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="F178" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="G178" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="H178" t="s">
         <v>13</v>
@@ -7347,22 +7360,22 @@
         <v>8</v>
       </c>
       <c r="B179" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="C179" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="D179" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="E179" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="F179" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="G179" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="H179" t="s">
         <v>13</v>
@@ -7373,22 +7386,22 @@
         <v>8</v>
       </c>
       <c r="B180" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="C180" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="D180" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="E180" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="F180" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="G180" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="H180" t="s">
         <v>13</v>
@@ -7399,22 +7412,22 @@
         <v>8</v>
       </c>
       <c r="B181" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="C181" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="D181" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="E181" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="F181" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="G181" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="H181" t="s">
         <v>13</v>
@@ -7425,22 +7438,22 @@
         <v>8</v>
       </c>
       <c r="B182" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="C182" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="D182" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="E182" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="F182" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="G182" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="H182" t="s">
         <v>13</v>
@@ -7451,22 +7464,22 @@
         <v>8</v>
       </c>
       <c r="B183" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="C183" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="D183" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="E183" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="F183" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="G183" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="H183" t="s">
         <v>13</v>
@@ -7477,16 +7490,16 @@
         <v>8</v>
       </c>
       <c r="B184" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="C184" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="D184" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="E184" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="F184" t="s">
         <v>439</v>
@@ -7503,22 +7516,22 @@
         <v>8</v>
       </c>
       <c r="B185" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="C185" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="D185" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="E185" t="s">
         <v>441</v>
       </c>
       <c r="F185" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="G185" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="H185" t="s">
         <v>13</v>
@@ -7529,22 +7542,22 @@
         <v>8</v>
       </c>
       <c r="B186" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="C186" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="D186" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="E186" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="F186" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="G186" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="H186" t="s">
         <v>13</v>
@@ -7555,22 +7568,22 @@
         <v>8</v>
       </c>
       <c r="B187" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="C187" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="D187" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="E187" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="F187" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="G187" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="H187" t="s">
         <v>13</v>
@@ -7581,22 +7594,22 @@
         <v>8</v>
       </c>
       <c r="B188" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="C188" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="D188" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="E188" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="F188" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="G188" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="H188" t="s">
         <v>13</v>
@@ -7607,16 +7620,16 @@
         <v>8</v>
       </c>
       <c r="B189" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="C189" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="D189" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="E189" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="F189" t="s">
         <v>451</v>
@@ -7625,7 +7638,7 @@
         <v>452</v>
       </c>
       <c r="H189" t="s">
-        <v>13</v>
+        <v>59</v>
       </c>
     </row>
     <row r="190" spans="1:8" x14ac:dyDescent="0.35">
@@ -7633,13 +7646,13 @@
         <v>8</v>
       </c>
       <c r="B190" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="C190" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="D190" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="E190" t="s">
         <v>453</v>
@@ -7651,7 +7664,7 @@
         <v>454</v>
       </c>
       <c r="H190" t="s">
-        <v>13</v>
+        <v>59</v>
       </c>
     </row>
     <row r="191" spans="1:8" x14ac:dyDescent="0.35">
@@ -7659,13 +7672,13 @@
         <v>8</v>
       </c>
       <c r="B191" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="C191" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="D191" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="E191" t="s">
         <v>455</v>
@@ -7685,13 +7698,13 @@
         <v>8</v>
       </c>
       <c r="B192" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="C192" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="D192" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="E192" t="s">
         <v>457</v>
@@ -7711,13 +7724,13 @@
         <v>8</v>
       </c>
       <c r="B193" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="C193" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="D193" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="E193" t="s">
         <v>459</v>
@@ -7737,13 +7750,13 @@
         <v>8</v>
       </c>
       <c r="B194" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="C194" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="D194" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="E194" t="s">
         <v>461</v>
@@ -7763,13 +7776,13 @@
         <v>8</v>
       </c>
       <c r="B195" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="C195" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="D195" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="E195" t="s">
         <v>463</v>
@@ -7789,13 +7802,13 @@
         <v>8</v>
       </c>
       <c r="B196" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="C196" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="D196" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="E196" t="s">
         <v>465</v>
@@ -7815,13 +7828,13 @@
         <v>8</v>
       </c>
       <c r="B197" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="C197" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="D197" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="E197" t="s">
         <v>467</v>
@@ -7841,13 +7854,13 @@
         <v>8</v>
       </c>
       <c r="B198" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="C198" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="D198" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="E198" t="s">
         <v>469</v>
@@ -7867,13 +7880,13 @@
         <v>8</v>
       </c>
       <c r="B199" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="C199" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="D199" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="E199" t="s">
         <v>471</v>
@@ -7890,54 +7903,54 @@
     </row>
     <row r="200" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A200">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B200" t="s">
-        <v>401</v>
+        <v>207</v>
       </c>
       <c r="C200" t="s">
-        <v>402</v>
+        <v>473</v>
       </c>
       <c r="D200" t="s">
-        <v>403</v>
+        <v>474</v>
       </c>
       <c r="E200" t="s">
-        <v>473</v>
+        <v>11</v>
       </c>
       <c r="F200" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="G200" t="s">
-        <v>474</v>
+        <v>12</v>
       </c>
       <c r="H200" t="s">
-        <v>59</v>
+        <v>13</v>
       </c>
     </row>
     <row r="201" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A201">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B201" t="s">
-        <v>401</v>
+        <v>207</v>
       </c>
       <c r="C201" t="s">
-        <v>402</v>
+        <v>473</v>
       </c>
       <c r="D201" t="s">
-        <v>403</v>
+        <v>474</v>
       </c>
       <c r="E201" t="s">
-        <v>475</v>
+        <v>237</v>
       </c>
       <c r="F201" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="G201" t="s">
-        <v>476</v>
+        <v>238</v>
       </c>
       <c r="H201" t="s">
-        <v>59</v>
+        <v>13</v>
       </c>
     </row>
     <row r="202" spans="1:8" x14ac:dyDescent="0.35">
@@ -7948,19 +7961,19 @@
         <v>207</v>
       </c>
       <c r="C202" t="s">
+        <v>473</v>
+      </c>
+      <c r="D202" t="s">
+        <v>474</v>
+      </c>
+      <c r="E202" t="s">
         <v>477</v>
       </c>
-      <c r="D202" t="s">
+      <c r="F202" t="s">
+        <v>477</v>
+      </c>
+      <c r="G202" t="s">
         <v>478</v>
-      </c>
-      <c r="E202" t="s">
-        <v>11</v>
-      </c>
-      <c r="F202" t="s">
-        <v>479</v>
-      </c>
-      <c r="G202" t="s">
-        <v>12</v>
       </c>
       <c r="H202" t="s">
         <v>13</v>
@@ -7974,19 +7987,19 @@
         <v>207</v>
       </c>
       <c r="C203" t="s">
-        <v>477</v>
+        <v>473</v>
       </c>
       <c r="D203" t="s">
-        <v>478</v>
+        <v>474</v>
       </c>
       <c r="E203" t="s">
-        <v>237</v>
+        <v>150</v>
       </c>
       <c r="F203" t="s">
-        <v>480</v>
+        <v>400</v>
       </c>
       <c r="G203" t="s">
-        <v>238</v>
+        <v>151</v>
       </c>
       <c r="H203" t="s">
         <v>13</v>
@@ -8000,19 +8013,19 @@
         <v>207</v>
       </c>
       <c r="C204" t="s">
-        <v>477</v>
+        <v>473</v>
       </c>
       <c r="D204" t="s">
-        <v>478</v>
+        <v>474</v>
       </c>
       <c r="E204" t="s">
-        <v>481</v>
+        <v>401</v>
       </c>
       <c r="F204" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="G204" t="s">
-        <v>482</v>
+        <v>403</v>
       </c>
       <c r="H204" t="s">
         <v>13</v>
@@ -8026,19 +8039,19 @@
         <v>207</v>
       </c>
       <c r="C205" t="s">
-        <v>477</v>
+        <v>473</v>
       </c>
       <c r="D205" t="s">
-        <v>478</v>
+        <v>474</v>
       </c>
       <c r="E205" t="s">
-        <v>150</v>
+        <v>480</v>
       </c>
       <c r="F205" t="s">
-        <v>404</v>
+        <v>480</v>
       </c>
       <c r="G205" t="s">
-        <v>151</v>
+        <v>481</v>
       </c>
       <c r="H205" t="s">
         <v>13</v>
@@ -8052,19 +8065,19 @@
         <v>207</v>
       </c>
       <c r="C206" t="s">
-        <v>477</v>
+        <v>473</v>
       </c>
       <c r="D206" t="s">
-        <v>478</v>
+        <v>474</v>
       </c>
       <c r="E206" t="s">
-        <v>405</v>
+        <v>482</v>
       </c>
       <c r="F206" t="s">
+        <v>482</v>
+      </c>
+      <c r="G206" t="s">
         <v>483</v>
-      </c>
-      <c r="G206" t="s">
-        <v>407</v>
       </c>
       <c r="H206" t="s">
         <v>13</v>
@@ -8078,10 +8091,10 @@
         <v>207</v>
       </c>
       <c r="C207" t="s">
-        <v>477</v>
+        <v>473</v>
       </c>
       <c r="D207" t="s">
-        <v>478</v>
+        <v>474</v>
       </c>
       <c r="E207" t="s">
         <v>484</v>
@@ -8093,7 +8106,7 @@
         <v>485</v>
       </c>
       <c r="H207" t="s">
-        <v>13</v>
+        <v>178</v>
       </c>
     </row>
     <row r="208" spans="1:8" x14ac:dyDescent="0.35">
@@ -8104,10 +8117,10 @@
         <v>207</v>
       </c>
       <c r="C208" t="s">
-        <v>477</v>
+        <v>473</v>
       </c>
       <c r="D208" t="s">
-        <v>478</v>
+        <v>474</v>
       </c>
       <c r="E208" t="s">
         <v>486</v>
@@ -8119,7 +8132,7 @@
         <v>487</v>
       </c>
       <c r="H208" t="s">
-        <v>13</v>
+        <v>178</v>
       </c>
     </row>
     <row r="209" spans="1:8" x14ac:dyDescent="0.35">
@@ -8130,10 +8143,10 @@
         <v>207</v>
       </c>
       <c r="C209" t="s">
-        <v>477</v>
+        <v>473</v>
       </c>
       <c r="D209" t="s">
-        <v>478</v>
+        <v>474</v>
       </c>
       <c r="E209" t="s">
         <v>488</v>
@@ -8145,7 +8158,7 @@
         <v>489</v>
       </c>
       <c r="H209" t="s">
-        <v>178</v>
+        <v>13</v>
       </c>
     </row>
     <row r="210" spans="1:8" x14ac:dyDescent="0.35">
@@ -8156,22 +8169,22 @@
         <v>207</v>
       </c>
       <c r="C210" t="s">
-        <v>477</v>
+        <v>473</v>
       </c>
       <c r="D210" t="s">
-        <v>478</v>
+        <v>474</v>
       </c>
       <c r="E210" t="s">
         <v>490</v>
       </c>
       <c r="F210" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="G210" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="H210" t="s">
-        <v>178</v>
+        <v>13</v>
       </c>
     </row>
     <row r="211" spans="1:8" x14ac:dyDescent="0.35">
@@ -8182,19 +8195,19 @@
         <v>207</v>
       </c>
       <c r="C211" t="s">
-        <v>477</v>
+        <v>473</v>
       </c>
       <c r="D211" t="s">
-        <v>478</v>
+        <v>474</v>
       </c>
       <c r="E211" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="F211" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="G211" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="H211" t="s">
         <v>13</v>
@@ -8208,19 +8221,19 @@
         <v>207</v>
       </c>
       <c r="C212" t="s">
-        <v>477</v>
+        <v>473</v>
       </c>
       <c r="D212" t="s">
-        <v>478</v>
+        <v>474</v>
       </c>
       <c r="E212" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="F212" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="G212" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="H212" t="s">
         <v>13</v>
@@ -8234,19 +8247,19 @@
         <v>207</v>
       </c>
       <c r="C213" t="s">
-        <v>477</v>
+        <v>473</v>
       </c>
       <c r="D213" t="s">
-        <v>478</v>
+        <v>474</v>
       </c>
       <c r="E213" t="s">
-        <v>497</v>
+        <v>424</v>
       </c>
       <c r="F213" t="s">
         <v>498</v>
       </c>
       <c r="G213" t="s">
-        <v>499</v>
+        <v>425</v>
       </c>
       <c r="H213" t="s">
         <v>13</v>
@@ -8260,19 +8273,19 @@
         <v>207</v>
       </c>
       <c r="C214" t="s">
-        <v>477</v>
+        <v>473</v>
       </c>
       <c r="D214" t="s">
-        <v>478</v>
+        <v>474</v>
       </c>
       <c r="E214" t="s">
-        <v>500</v>
+        <v>437</v>
       </c>
       <c r="F214" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="G214" t="s">
-        <v>501</v>
+        <v>438</v>
       </c>
       <c r="H214" t="s">
         <v>13</v>
@@ -8286,19 +8299,19 @@
         <v>207</v>
       </c>
       <c r="C215" t="s">
-        <v>477</v>
+        <v>473</v>
       </c>
       <c r="D215" t="s">
-        <v>478</v>
+        <v>474</v>
       </c>
       <c r="E215" t="s">
-        <v>428</v>
+        <v>500</v>
       </c>
       <c r="F215" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="G215" t="s">
-        <v>429</v>
+        <v>501</v>
       </c>
       <c r="H215" t="s">
         <v>13</v>
@@ -8312,22 +8325,22 @@
         <v>207</v>
       </c>
       <c r="C216" t="s">
-        <v>477</v>
+        <v>473</v>
       </c>
       <c r="D216" t="s">
-        <v>478</v>
+        <v>474</v>
       </c>
       <c r="E216" t="s">
-        <v>441</v>
+        <v>502</v>
       </c>
       <c r="F216" t="s">
+        <v>502</v>
+      </c>
+      <c r="G216" t="s">
         <v>503</v>
       </c>
-      <c r="G216" t="s">
-        <v>442</v>
-      </c>
       <c r="H216" t="s">
-        <v>13</v>
+        <v>59</v>
       </c>
     </row>
     <row r="217" spans="1:8" x14ac:dyDescent="0.35">
@@ -8338,10 +8351,10 @@
         <v>207</v>
       </c>
       <c r="C217" t="s">
-        <v>477</v>
+        <v>473</v>
       </c>
       <c r="D217" t="s">
-        <v>478</v>
+        <v>474</v>
       </c>
       <c r="E217" t="s">
         <v>504</v>
@@ -8353,7 +8366,7 @@
         <v>505</v>
       </c>
       <c r="H217" t="s">
-        <v>13</v>
+        <v>59</v>
       </c>
     </row>
     <row r="218" spans="1:8" x14ac:dyDescent="0.35">
@@ -8364,10 +8377,10 @@
         <v>207</v>
       </c>
       <c r="C218" t="s">
-        <v>477</v>
+        <v>473</v>
       </c>
       <c r="D218" t="s">
-        <v>478</v>
+        <v>474</v>
       </c>
       <c r="E218" t="s">
         <v>506</v>
@@ -8390,10 +8403,10 @@
         <v>207</v>
       </c>
       <c r="C219" t="s">
-        <v>477</v>
+        <v>473</v>
       </c>
       <c r="D219" t="s">
-        <v>478</v>
+        <v>474</v>
       </c>
       <c r="E219" t="s">
         <v>508</v>
@@ -8416,19 +8429,19 @@
         <v>207</v>
       </c>
       <c r="C220" t="s">
-        <v>477</v>
+        <v>473</v>
       </c>
       <c r="D220" t="s">
-        <v>478</v>
+        <v>474</v>
       </c>
       <c r="E220" t="s">
-        <v>510</v>
+        <v>222</v>
       </c>
       <c r="F220" t="s">
-        <v>510</v>
+        <v>315</v>
       </c>
       <c r="G220" t="s">
-        <v>511</v>
+        <v>223</v>
       </c>
       <c r="H220" t="s">
         <v>59</v>
@@ -8442,19 +8455,19 @@
         <v>207</v>
       </c>
       <c r="C221" t="s">
-        <v>477</v>
+        <v>473</v>
       </c>
       <c r="D221" t="s">
-        <v>478</v>
+        <v>474</v>
       </c>
       <c r="E221" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="F221" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="G221" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="H221" t="s">
         <v>59</v>
@@ -8468,19 +8481,19 @@
         <v>207</v>
       </c>
       <c r="C222" t="s">
-        <v>477</v>
+        <v>473</v>
       </c>
       <c r="D222" t="s">
-        <v>478</v>
+        <v>474</v>
       </c>
       <c r="E222" t="s">
-        <v>222</v>
+        <v>512</v>
       </c>
       <c r="F222" t="s">
-        <v>317</v>
+        <v>512</v>
       </c>
       <c r="G222" t="s">
-        <v>223</v>
+        <v>513</v>
       </c>
       <c r="H222" t="s">
         <v>59</v>
@@ -8494,10 +8507,10 @@
         <v>207</v>
       </c>
       <c r="C223" t="s">
-        <v>477</v>
+        <v>473</v>
       </c>
       <c r="D223" t="s">
-        <v>478</v>
+        <v>474</v>
       </c>
       <c r="E223" t="s">
         <v>514</v>
@@ -8520,10 +8533,10 @@
         <v>207</v>
       </c>
       <c r="C224" t="s">
-        <v>477</v>
+        <v>473</v>
       </c>
       <c r="D224" t="s">
-        <v>478</v>
+        <v>474</v>
       </c>
       <c r="E224" t="s">
         <v>516</v>
@@ -8546,10 +8559,10 @@
         <v>207</v>
       </c>
       <c r="C225" t="s">
-        <v>477</v>
+        <v>473</v>
       </c>
       <c r="D225" t="s">
-        <v>478</v>
+        <v>474</v>
       </c>
       <c r="E225" t="s">
         <v>518</v>
@@ -8566,54 +8579,54 @@
     </row>
     <row r="226" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A226">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B226" t="s">
+        <v>207</v>
+      </c>
+      <c r="C226" t="s">
+        <v>473</v>
+      </c>
+      <c r="D226" t="s">
+        <v>474</v>
+      </c>
+      <c r="E226" t="s">
         <v>520</v>
       </c>
-      <c r="C226" t="s">
+      <c r="F226" t="s">
+        <v>520</v>
+      </c>
+      <c r="G226" t="s">
         <v>521</v>
       </c>
-      <c r="D226" t="s">
-        <v>522</v>
-      </c>
-      <c r="E226" t="s">
-        <v>523</v>
-      </c>
-      <c r="F226" t="s">
-        <v>523</v>
-      </c>
-      <c r="G226" t="s">
-        <v>524</v>
-      </c>
       <c r="H226" t="s">
-        <v>13</v>
+        <v>59</v>
       </c>
     </row>
     <row r="227" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A227">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B227" t="s">
-        <v>520</v>
+        <v>207</v>
       </c>
       <c r="C227" t="s">
-        <v>521</v>
+        <v>473</v>
       </c>
       <c r="D227" t="s">
+        <v>474</v>
+      </c>
+      <c r="E227" t="s">
         <v>522</v>
       </c>
-      <c r="E227" t="s">
-        <v>525</v>
-      </c>
       <c r="F227" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="G227" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="H227" t="s">
-        <v>13</v>
+        <v>59</v>
       </c>
     </row>
     <row r="228" spans="1:8" x14ac:dyDescent="0.35">
@@ -8621,13 +8634,13 @@
         <v>10</v>
       </c>
       <c r="B228" t="s">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="C228" t="s">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="D228" t="s">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="E228" t="s">
         <v>527</v>
@@ -8647,13 +8660,13 @@
         <v>10</v>
       </c>
       <c r="B229" t="s">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="C229" t="s">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="D229" t="s">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="E229" t="s">
         <v>529</v>
@@ -8673,13 +8686,13 @@
         <v>10</v>
       </c>
       <c r="B230" t="s">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="C230" t="s">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="D230" t="s">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="E230" t="s">
         <v>531</v>
@@ -8699,22 +8712,22 @@
         <v>10</v>
       </c>
       <c r="B231" t="s">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="C231" t="s">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="D231" t="s">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="E231" t="s">
         <v>533</v>
       </c>
       <c r="F231" t="s">
+        <v>533</v>
+      </c>
+      <c r="G231" t="s">
         <v>534</v>
-      </c>
-      <c r="G231" t="s">
-        <v>535</v>
       </c>
       <c r="H231" t="s">
         <v>13</v>
@@ -8725,22 +8738,22 @@
         <v>10</v>
       </c>
       <c r="B232" t="s">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="C232" t="s">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="D232" t="s">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="E232" t="s">
+        <v>535</v>
+      </c>
+      <c r="F232" t="s">
+        <v>535</v>
+      </c>
+      <c r="G232" t="s">
         <v>536</v>
-      </c>
-      <c r="F232" t="s">
-        <v>537</v>
-      </c>
-      <c r="G232" t="s">
-        <v>538</v>
       </c>
       <c r="H232" t="s">
         <v>13</v>
@@ -8751,25 +8764,25 @@
         <v>10</v>
       </c>
       <c r="B233" t="s">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="C233" t="s">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="D233" t="s">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="E233" t="s">
+        <v>537</v>
+      </c>
+      <c r="F233" t="s">
+        <v>538</v>
+      </c>
+      <c r="G233" t="s">
         <v>539</v>
       </c>
-      <c r="F233" t="s">
-        <v>540</v>
-      </c>
-      <c r="G233" t="s">
-        <v>541</v>
-      </c>
       <c r="H233" t="s">
-        <v>178</v>
+        <v>13</v>
       </c>
     </row>
     <row r="234" spans="1:8" x14ac:dyDescent="0.35">
@@ -8777,22 +8790,22 @@
         <v>10</v>
       </c>
       <c r="B234" t="s">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="C234" t="s">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="D234" t="s">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="E234" t="s">
+        <v>540</v>
+      </c>
+      <c r="F234" t="s">
+        <v>541</v>
+      </c>
+      <c r="G234" t="s">
         <v>542</v>
-      </c>
-      <c r="F234" t="s">
-        <v>543</v>
-      </c>
-      <c r="G234" t="s">
-        <v>544</v>
       </c>
       <c r="H234" t="s">
         <v>13</v>
@@ -8803,25 +8816,25 @@
         <v>10</v>
       </c>
       <c r="B235" t="s">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="C235" t="s">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="D235" t="s">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="E235" t="s">
+        <v>543</v>
+      </c>
+      <c r="F235" t="s">
+        <v>544</v>
+      </c>
+      <c r="G235" t="s">
         <v>545</v>
       </c>
-      <c r="F235" t="s">
-        <v>546</v>
-      </c>
-      <c r="G235" t="s">
-        <v>547</v>
-      </c>
       <c r="H235" t="s">
-        <v>13</v>
+        <v>178</v>
       </c>
     </row>
     <row r="236" spans="1:8" x14ac:dyDescent="0.35">
@@ -8829,22 +8842,22 @@
         <v>10</v>
       </c>
       <c r="B236" t="s">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="C236" t="s">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="D236" t="s">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="E236" t="s">
+        <v>546</v>
+      </c>
+      <c r="F236" t="s">
+        <v>547</v>
+      </c>
+      <c r="G236" t="s">
         <v>548</v>
-      </c>
-      <c r="F236" t="s">
-        <v>549</v>
-      </c>
-      <c r="G236" t="s">
-        <v>550</v>
       </c>
       <c r="H236" t="s">
         <v>13</v>
@@ -8855,22 +8868,22 @@
         <v>10</v>
       </c>
       <c r="B237" t="s">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="C237" t="s">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="D237" t="s">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="E237" t="s">
+        <v>549</v>
+      </c>
+      <c r="F237" t="s">
+        <v>550</v>
+      </c>
+      <c r="G237" t="s">
         <v>551</v>
-      </c>
-      <c r="F237" t="s">
-        <v>552</v>
-      </c>
-      <c r="G237" t="s">
-        <v>553</v>
       </c>
       <c r="H237" t="s">
         <v>13</v>
@@ -8881,22 +8894,22 @@
         <v>10</v>
       </c>
       <c r="B238" t="s">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="C238" t="s">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="D238" t="s">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="E238" t="s">
+        <v>552</v>
+      </c>
+      <c r="F238" t="s">
+        <v>553</v>
+      </c>
+      <c r="G238" t="s">
         <v>554</v>
-      </c>
-      <c r="F238" t="s">
-        <v>555</v>
-      </c>
-      <c r="G238" t="s">
-        <v>556</v>
       </c>
       <c r="H238" t="s">
         <v>13</v>
@@ -8907,22 +8920,22 @@
         <v>10</v>
       </c>
       <c r="B239" t="s">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="C239" t="s">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="D239" t="s">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="E239" t="s">
+        <v>555</v>
+      </c>
+      <c r="F239" t="s">
+        <v>556</v>
+      </c>
+      <c r="G239" t="s">
         <v>557</v>
-      </c>
-      <c r="F239" t="s">
-        <v>558</v>
-      </c>
-      <c r="G239" t="s">
-        <v>559</v>
       </c>
       <c r="H239" t="s">
         <v>13</v>
@@ -8933,22 +8946,22 @@
         <v>10</v>
       </c>
       <c r="B240" t="s">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="C240" t="s">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="D240" t="s">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="E240" t="s">
+        <v>558</v>
+      </c>
+      <c r="F240" t="s">
+        <v>559</v>
+      </c>
+      <c r="G240" t="s">
         <v>560</v>
-      </c>
-      <c r="F240" t="s">
-        <v>560</v>
-      </c>
-      <c r="G240" t="s">
-        <v>561</v>
       </c>
       <c r="H240" t="s">
         <v>13</v>
@@ -8959,16 +8972,16 @@
         <v>10</v>
       </c>
       <c r="B241" t="s">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="C241" t="s">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="D241" t="s">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="E241" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="F241" t="s">
         <v>562</v>
@@ -8985,13 +8998,13 @@
         <v>10</v>
       </c>
       <c r="B242" t="s">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="C242" t="s">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="D242" t="s">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="E242" t="s">
         <v>564</v>
@@ -9011,13 +9024,13 @@
         <v>10</v>
       </c>
       <c r="B243" t="s">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="C243" t="s">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="D243" t="s">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="E243" t="s">
         <v>566</v>
@@ -9037,22 +9050,22 @@
         <v>10</v>
       </c>
       <c r="B244" t="s">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="C244" t="s">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="D244" t="s">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="E244" t="s">
         <v>568</v>
       </c>
       <c r="F244" t="s">
+        <v>568</v>
+      </c>
+      <c r="G244" t="s">
         <v>569</v>
-      </c>
-      <c r="G244" t="s">
-        <v>570</v>
       </c>
       <c r="H244" t="s">
         <v>13</v>
@@ -9063,22 +9076,22 @@
         <v>10</v>
       </c>
       <c r="B245" t="s">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="C245" t="s">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="D245" t="s">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="E245" t="s">
+        <v>570</v>
+      </c>
+      <c r="F245" t="s">
+        <v>570</v>
+      </c>
+      <c r="G245" t="s">
         <v>571</v>
-      </c>
-      <c r="F245" t="s">
-        <v>572</v>
-      </c>
-      <c r="G245" t="s">
-        <v>573</v>
       </c>
       <c r="H245" t="s">
         <v>13</v>
@@ -9089,22 +9102,22 @@
         <v>10</v>
       </c>
       <c r="B246" t="s">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="C246" t="s">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="D246" t="s">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="E246" t="s">
+        <v>572</v>
+      </c>
+      <c r="F246" t="s">
+        <v>573</v>
+      </c>
+      <c r="G246" t="s">
         <v>574</v>
-      </c>
-      <c r="F246" t="s">
-        <v>575</v>
-      </c>
-      <c r="G246" t="s">
-        <v>576</v>
       </c>
       <c r="H246" t="s">
         <v>13</v>
@@ -9115,22 +9128,22 @@
         <v>10</v>
       </c>
       <c r="B247" t="s">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="C247" t="s">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="D247" t="s">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="E247" t="s">
+        <v>575</v>
+      </c>
+      <c r="F247" t="s">
+        <v>576</v>
+      </c>
+      <c r="G247" t="s">
         <v>577</v>
-      </c>
-      <c r="F247" t="s">
-        <v>578</v>
-      </c>
-      <c r="G247" t="s">
-        <v>579</v>
       </c>
       <c r="H247" t="s">
         <v>13</v>
@@ -9141,22 +9154,22 @@
         <v>10</v>
       </c>
       <c r="B248" t="s">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="C248" t="s">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="D248" t="s">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="E248" t="s">
+        <v>578</v>
+      </c>
+      <c r="F248" t="s">
+        <v>579</v>
+      </c>
+      <c r="G248" t="s">
         <v>580</v>
-      </c>
-      <c r="F248" t="s">
-        <v>581</v>
-      </c>
-      <c r="G248" t="s">
-        <v>582</v>
       </c>
       <c r="H248" t="s">
         <v>13</v>
@@ -9167,22 +9180,22 @@
         <v>10</v>
       </c>
       <c r="B249" t="s">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="C249" t="s">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="D249" t="s">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="E249" t="s">
+        <v>581</v>
+      </c>
+      <c r="F249" t="s">
+        <v>582</v>
+      </c>
+      <c r="G249" t="s">
         <v>583</v>
-      </c>
-      <c r="F249" t="s">
-        <v>584</v>
-      </c>
-      <c r="G249" t="s">
-        <v>585</v>
       </c>
       <c r="H249" t="s">
         <v>13</v>
@@ -9193,22 +9206,22 @@
         <v>10</v>
       </c>
       <c r="B250" t="s">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="C250" t="s">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="D250" t="s">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="E250" t="s">
+        <v>584</v>
+      </c>
+      <c r="F250" t="s">
+        <v>585</v>
+      </c>
+      <c r="G250" t="s">
         <v>586</v>
-      </c>
-      <c r="F250" t="s">
-        <v>587</v>
-      </c>
-      <c r="G250" t="s">
-        <v>588</v>
       </c>
       <c r="H250" t="s">
         <v>13</v>
@@ -9219,22 +9232,22 @@
         <v>10</v>
       </c>
       <c r="B251" t="s">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="C251" t="s">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="D251" t="s">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="E251" t="s">
+        <v>587</v>
+      </c>
+      <c r="F251" t="s">
+        <v>588</v>
+      </c>
+      <c r="G251" t="s">
         <v>589</v>
-      </c>
-      <c r="F251" t="s">
-        <v>590</v>
-      </c>
-      <c r="G251" t="s">
-        <v>591</v>
       </c>
       <c r="H251" t="s">
         <v>13</v>
@@ -9245,22 +9258,22 @@
         <v>10</v>
       </c>
       <c r="B252" t="s">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="C252" t="s">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="D252" t="s">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="E252" t="s">
+        <v>590</v>
+      </c>
+      <c r="F252" t="s">
+        <v>591</v>
+      </c>
+      <c r="G252" t="s">
         <v>592</v>
-      </c>
-      <c r="F252" t="s">
-        <v>593</v>
-      </c>
-      <c r="G252" t="s">
-        <v>594</v>
       </c>
       <c r="H252" t="s">
         <v>13</v>
@@ -9271,22 +9284,22 @@
         <v>10</v>
       </c>
       <c r="B253" t="s">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="C253" t="s">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="D253" t="s">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="E253" t="s">
+        <v>593</v>
+      </c>
+      <c r="F253" t="s">
+        <v>594</v>
+      </c>
+      <c r="G253" t="s">
         <v>595</v>
-      </c>
-      <c r="F253" t="s">
-        <v>596</v>
-      </c>
-      <c r="G253" t="s">
-        <v>597</v>
       </c>
       <c r="H253" t="s">
         <v>13</v>
@@ -9297,24 +9310,76 @@
         <v>10</v>
       </c>
       <c r="B254" t="s">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="C254" t="s">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="D254" t="s">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="E254" t="s">
+        <v>596</v>
+      </c>
+      <c r="F254" t="s">
+        <v>597</v>
+      </c>
+      <c r="G254" t="s">
         <v>598</v>
       </c>
-      <c r="F254" t="s">
-        <v>598</v>
-      </c>
-      <c r="G254" t="s">
+      <c r="H254" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="255" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A255">
+        <v>10</v>
+      </c>
+      <c r="B255" t="s">
+        <v>524</v>
+      </c>
+      <c r="C255" t="s">
+        <v>525</v>
+      </c>
+      <c r="D255" t="s">
+        <v>526</v>
+      </c>
+      <c r="E255" t="s">
         <v>599</v>
       </c>
-      <c r="H254" t="s">
+      <c r="F255" t="s">
+        <v>600</v>
+      </c>
+      <c r="G255" t="s">
+        <v>601</v>
+      </c>
+      <c r="H255" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="256" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A256">
+        <v>10</v>
+      </c>
+      <c r="B256" t="s">
+        <v>524</v>
+      </c>
+      <c r="C256" t="s">
+        <v>525</v>
+      </c>
+      <c r="D256" t="s">
+        <v>526</v>
+      </c>
+      <c r="E256" t="s">
+        <v>602</v>
+      </c>
+      <c r="F256" t="s">
+        <v>602</v>
+      </c>
+      <c r="G256" t="s">
+        <v>603</v>
+      </c>
+      <c r="H256" t="s">
         <v>13</v>
       </c>
     </row>
